--- a/product_selector_out/STM32F7x7.xlsx
+++ b/product_selector_out/STM32F7x7.xlsx
@@ -11831,7 +11831,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -11941,7 +11941,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -12095,7 +12095,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -12227,7 +12227,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -12381,7 +12381,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -12557,7 +12557,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -12689,7 +12689,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -12799,7 +12799,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -12953,7 +12953,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -13085,7 +13085,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -13195,7 +13195,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -13305,7 +13305,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -13415,7 +13415,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -13569,7 +13569,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -13701,7 +13701,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>

--- a/product_selector_out/STM32F7x7.xlsx
+++ b/product_selector_out/STM32F7x7.xlsx
@@ -7473,9 +7473,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB14" s="8" t="inlineStr">
@@ -8147,9 +8147,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA16" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB16" s="8" t="inlineStr">
@@ -8484,9 +8484,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA17" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB17" s="8" t="inlineStr">
@@ -9495,9 +9495,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA20" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB20" s="8" t="inlineStr">
@@ -11180,9 +11180,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA25" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB25" s="8" t="inlineStr">

--- a/product_selector_out/STM32F7x7.xlsx
+++ b/product_selector_out/STM32F7x7.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO26"/>
+  <dimension ref="A1:BP26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.61328125" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,8 @@
     <col width="21.765625" customWidth="1" min="64" max="64"/>
     <col width="18" customWidth="1" min="65" max="65"/>
     <col width="18" customWidth="1" min="66" max="66"/>
-    <col width="52" customWidth="1" min="67" max="67"/>
+    <col width="18" customWidth="1" min="67" max="67"/>
+    <col width="52" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -907,6 +908,11 @@
         </is>
       </c>
       <c r="BO10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BP10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -1004,6 +1010,7 @@
       <c r="BM11" s="2" t="n"/>
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
+      <c r="BP11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1338,6 +1345,11 @@
       </c>
       <c r="BO12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f765bg.pdf</t>
         </is>
       </c>
@@ -1675,6 +1687,11 @@
       </c>
       <c r="BO13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f765bg.pdf</t>
         </is>
       </c>
@@ -2012,6 +2029,11 @@
       </c>
       <c r="BO14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f777bi.pdf</t>
         </is>
       </c>
@@ -2349,6 +2371,11 @@
       </c>
       <c r="BO15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f765bg.pdf</t>
         </is>
       </c>
@@ -2686,6 +2713,11 @@
       </c>
       <c r="BO16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f777bi.pdf</t>
         </is>
       </c>
@@ -3023,6 +3055,11 @@
       </c>
       <c r="BO17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f777bi.pdf</t>
         </is>
       </c>
@@ -3360,6 +3397,11 @@
       </c>
       <c r="BO18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f765bg.pdf</t>
         </is>
       </c>
@@ -3697,6 +3739,11 @@
       </c>
       <c r="BO19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f765bg.pdf</t>
         </is>
       </c>
@@ -4034,6 +4081,11 @@
       </c>
       <c r="BO20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f777bi.pdf</t>
         </is>
       </c>
@@ -4371,6 +4423,11 @@
       </c>
       <c r="BO21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f765bg.pdf</t>
         </is>
       </c>
@@ -4708,6 +4765,11 @@
       </c>
       <c r="BO22" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f765bg.pdf</t>
         </is>
       </c>
@@ -5045,6 +5107,11 @@
       </c>
       <c r="BO23" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f765bg.pdf</t>
         </is>
       </c>
@@ -5382,6 +5449,11 @@
       </c>
       <c r="BO24" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f765bg.pdf</t>
         </is>
       </c>
@@ -5719,6 +5791,11 @@
       </c>
       <c r="BO25" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP25" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f777bi.pdf</t>
         </is>
       </c>
@@ -6056,12 +6133,17 @@
       </c>
       <c r="BO26" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP26" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f765bg.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="66">
+  <mergeCells count="67">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -6084,12 +6166,14 @@
     <mergeCell ref="Q10:Q11"/>
     <mergeCell ref="AR10:AR11"/>
     <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="A9:BP9"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="A1:BP8"/>
     <mergeCell ref="AV10:AV11"/>
     <mergeCell ref="BB10:BB11"/>
+    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BD10:BD11"/>
     <mergeCell ref="BM10:BM11"/>
-    <mergeCell ref="BD10:BD11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -6104,9 +6188,8 @@
     <mergeCell ref="BH10:BH11"/>
     <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
-    <mergeCell ref="A1:BO8"/>
+    <mergeCell ref="BP10:BP11"/>
     <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="A9:BO9"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="I10:I11"/>
     <mergeCell ref="AL10:AL11"/>
@@ -6157,7 +6240,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO26"/>
+  <dimension ref="A1:BP26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6227,6 +6310,7 @@
     <col width="16" customWidth="1" min="65" max="65"/>
     <col width="16" customWidth="1" min="66" max="66"/>
     <col width="16" customWidth="1" min="67" max="67"/>
+    <col width="16" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6570,6 +6654,11 @@
         </is>
       </c>
       <c r="BO10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BP10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -6667,6 +6756,7 @@
       <c r="BM11" s="2" t="n"/>
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
+      <c r="BP11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -6999,7 +7089,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO12" s="6" t="inlineStr">
+      <c r="BO12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7336,7 +7431,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO13" s="6" t="inlineStr">
+      <c r="BO13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7673,7 +7773,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO14" s="6" t="inlineStr">
+      <c r="BO14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8010,7 +8115,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO15" s="6" t="inlineStr">
+      <c r="BO15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8347,7 +8457,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO16" s="6" t="inlineStr">
+      <c r="BO16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8684,7 +8799,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO17" s="6" t="inlineStr">
+      <c r="BO17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9021,7 +9141,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO18" s="6" t="inlineStr">
+      <c r="BO18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9358,7 +9483,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO19" s="6" t="inlineStr">
+      <c r="BO19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9695,7 +9825,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO20" s="6" t="inlineStr">
+      <c r="BO20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10032,7 +10167,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO21" s="6" t="inlineStr">
+      <c r="BO21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10369,7 +10509,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO22" s="6" t="inlineStr">
+      <c r="BO22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10706,7 +10851,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO23" s="6" t="inlineStr">
+      <c r="BO23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11043,7 +11193,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO24" s="6" t="inlineStr">
+      <c r="BO24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11380,7 +11535,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO25" s="6" t="inlineStr">
+      <c r="BO25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP25" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11717,7 +11877,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO26" s="6" t="inlineStr">
+      <c r="BO26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP26" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11725,8 +11890,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BO9"/>
-    <mergeCell ref="A1:BO8"/>
+    <mergeCell ref="A1:BP8"/>
+    <mergeCell ref="A9:BP9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
